--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13440"/>
+    <workbookView windowWidth="25600" windowHeight="10400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -492,11 +492,98 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="ID_F05DCBE9AA4948C1A4F8791A69F0466D"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18871565" y="12026900"/>
+          <a:ext cx="14516100" cy="8782050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="ID_05EEE1B1EC2C430FBAC6E707CF2F7ED1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18871565" y="12496800"/>
+          <a:ext cx="16383000" cy="3514725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="ID_8670CE2A04B84A3CBC23D16A2ACA0B53"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18871565" y="12966700"/>
+          <a:ext cx="13487400" cy="7058025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="82">
   <si>
     <t>Номер</t>
   </si>
@@ -721,6 +808,27 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>3.12</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>3.13</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>3.14</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>Неустойчивости нет, возможно разрешения не хватает</t>
   </si>
 </sst>
 </file>
@@ -1412,7 +1520,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1448,6 +1556,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1787,23 +1898,23 @@
   <dimension ref="A1:S36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="16.3333333333333" style="1" customWidth="1"/>
-    <col min="2" max="5" width="6.02777777777778" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6944444444444" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.2222222222222" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7037037037037" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34.5555555555556" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.4444444444444" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.3333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.4444444444444" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.3333333333333" style="1" customWidth="1"/>
-    <col min="14" max="14" width="27.5555555555556" style="1" customWidth="1"/>
-    <col min="15" max="15" width="31.4444444444444" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.4537037037037" style="1" customWidth="1"/>
-    <col min="17" max="17" width="81.2685185185185" style="1" customWidth="1"/>
-    <col min="18" max="18" width="63.2592592592593" style="1" customWidth="1"/>
-    <col min="19" max="21" width="16.3333333333333" style="1" customWidth="1"/>
-    <col min="22" max="27" width="16.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="16.3363636363636" style="1" customWidth="1"/>
+    <col min="2" max="5" width="6.02727272727273" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6909090909091" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.2181818181818" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7" style="1" customWidth="1"/>
+    <col min="9" max="9" width="34.5545454545455" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21.4454545454545" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.3363636363636" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.4454545454545" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16.3363636363636" style="1" customWidth="1"/>
+    <col min="14" max="14" width="27.5545454545455" style="1" customWidth="1"/>
+    <col min="15" max="15" width="31.4454545454545" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.4545454545455" style="1" customWidth="1"/>
+    <col min="17" max="17" width="81.2727272727273" style="1" customWidth="1"/>
+    <col min="18" max="18" width="63.2636363636364" style="1" customWidth="1"/>
+    <col min="19" max="21" width="16.3363636363636" style="1" customWidth="1"/>
+    <col min="22" max="27" width="16.3363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="79" customHeight="1" spans="1:17">
@@ -1924,10 +2035,10 @@
         <v>20</v>
       </c>
       <c r="P3" s="3"/>
-      <c r="R3" s="15" t="s">
+      <c r="R3" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="S3" s="16" t="str">
+      <c r="S3" s="17" t="str">
         <f>_xlfn.DISPIMG("ID_2DC6207669014A37BFB9BE39DC187DCE",1)</f>
         <v>=DISPIMG("ID_2DC6207669014A37BFB9BE39DC187DCE",1)</v>
       </c>
@@ -2006,7 +2117,7 @@
       <c r="O5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="13" t="str">
+      <c r="P5" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_AAAED62E82D54B409AB5C8B0C7DD6A82",1)</f>
         <v>=DISPIMG("ID_AAAED62E82D54B409AB5C8B0C7DD6A82",1)</v>
       </c>
@@ -2047,7 +2158,7 @@
       <c r="O6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P6" s="13" t="str">
+      <c r="P6" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_4CFD75D374CE4DDE9E03BA4DC092D744",1)</f>
         <v>=DISPIMG("ID_4CFD75D374CE4DDE9E03BA4DC092D744",1)</v>
       </c>
@@ -2088,11 +2199,11 @@
       <c r="O7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P7" s="13" t="str">
+      <c r="P7" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_6DCA3A3E153C4171953BC0544CE3C76A",1)</f>
         <v>=DISPIMG("ID_6DCA3A3E153C4171953BC0544CE3C76A",1)</v>
       </c>
-      <c r="Q7" s="17" t="s">
+      <c r="Q7" s="18" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2134,7 +2245,7 @@
       <c r="O8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P8" s="13" t="str">
+      <c r="P8" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_49006A477D2349A0BE5661F7511B2CBC",1)</f>
         <v>=DISPIMG("ID_49006A477D2349A0BE5661F7511B2CBC",1)</v>
       </c>
@@ -2178,7 +2289,7 @@
       <c r="O9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P9" s="13" t="str">
+      <c r="P9" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_4322BD9D201E4A40820FC7B99B813840",1)</f>
         <v>=DISPIMG("ID_4322BD9D201E4A40820FC7B99B813840",1)</v>
       </c>
@@ -2219,11 +2330,11 @@
       <c r="O10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P10" s="13" t="str">
+      <c r="P10" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_02B3F99283104BCBB532A5A0354AB72C",1)</f>
         <v>=DISPIMG("ID_02B3F99283104BCBB532A5A0354AB72C",1)</v>
       </c>
-      <c r="Q10" s="17" t="s">
+      <c r="Q10" s="18" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2263,11 +2374,11 @@
       <c r="O11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="P11" s="13" t="str">
+      <c r="P11" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_FE861988B73846E0B38C47E32EB5393F",1)</f>
         <v>=DISPIMG("ID_FE861988B73846E0B38C47E32EB5393F",1)</v>
       </c>
-      <c r="Q11" s="17"/>
+      <c r="Q11" s="18"/>
     </row>
     <row r="12" ht="37" customHeight="1" spans="1:16">
       <c r="A12" s="5" t="s">
@@ -2305,7 +2416,7 @@
       <c r="O12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="P12" s="13" t="str">
+      <c r="P12" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_B6639CE39850471191E748FA5694FB6F",1)</f>
         <v>=DISPIMG("ID_B6639CE39850471191E748FA5694FB6F",1)</v>
       </c>
@@ -2346,7 +2457,7 @@
       <c r="O13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P13" s="13" t="str">
+      <c r="P13" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_7C45C7571ED744B89C8B413974F434EA",1)</f>
         <v>=DISPIMG("ID_7C45C7571ED744B89C8B413974F434EA",1)</v>
       </c>
@@ -2390,7 +2501,7 @@
       <c r="O14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="P14" s="13" t="str">
+      <c r="P14" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_6D09333D2B624D3AA8D9D1DBAAFF6749",1)</f>
         <v>=DISPIMG("ID_6D09333D2B624D3AA8D9D1DBAAFF6749",1)</v>
       </c>
@@ -2581,7 +2692,7 @@
       <c r="O19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P19" s="13" t="str">
+      <c r="P19" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_F8652202BAD9483CA0345616A3ED7FD4",1)</f>
         <v>=DISPIMG("ID_F8652202BAD9483CA0345616A3ED7FD4",1)</v>
       </c>
@@ -2613,7 +2724,7 @@
       <c r="K20" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="L20" s="14" t="s">
+      <c r="L20" s="15" t="s">
         <v>68</v>
       </c>
       <c r="M20" s="3" t="s">
@@ -2625,7 +2736,7 @@
       <c r="O20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P20" s="13" t="str">
+      <c r="P20" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_3840878A904E4B56A2DD87192D35456F",1)</f>
         <v>=DISPIMG("ID_3840878A904E4B56A2DD87192D35456F",1)</v>
       </c>
@@ -2654,7 +2765,7 @@
       <c r="K21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="L21" s="14" t="s">
+      <c r="L21" s="15" t="s">
         <v>68</v>
       </c>
       <c r="M21" s="3" t="s">
@@ -2666,7 +2777,7 @@
       <c r="O21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P21" s="13" t="str">
+      <c r="P21" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_D3ACB0D6ED9E402EB08DE4311E6D85F2",1)</f>
         <v>=DISPIMG("ID_D3ACB0D6ED9E402EB08DE4311E6D85F2",1)</v>
       </c>
@@ -2698,7 +2809,7 @@
       <c r="K22" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="L22" s="14" t="s">
+      <c r="L22" s="15" t="s">
         <v>68</v>
       </c>
       <c r="M22" s="3" t="s">
@@ -2710,7 +2821,7 @@
       <c r="O22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P22" s="13" t="str">
+      <c r="P22" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_3A1B8F4BCF0C4B34AB3CE341C5ED6561",1)</f>
         <v>=DISPIMG("ID_3A1B8F4BCF0C4B34AB3CE341C5ED6561",1)</v>
       </c>
@@ -2739,7 +2850,7 @@
       <c r="K23" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="L23" s="14" t="s">
+      <c r="L23" s="15" t="s">
         <v>68</v>
       </c>
       <c r="M23" s="3" t="s">
@@ -2749,7 +2860,7 @@
         <v>19</v>
       </c>
       <c r="O23" s="3"/>
-      <c r="P23" s="13"/>
+      <c r="P23" s="14"/>
     </row>
     <row r="24" ht="37" customHeight="1" spans="1:16">
       <c r="A24" s="4" t="s">
@@ -2775,7 +2886,7 @@
       <c r="K24" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="L24" s="14" t="s">
+      <c r="L24" s="15" t="s">
         <v>68</v>
       </c>
       <c r="M24" s="3" t="s">
@@ -2785,64 +2896,132 @@
         <v>19</v>
       </c>
       <c r="O24" s="3"/>
-      <c r="P24" s="13" t="str">
+      <c r="P24" s="14" t="str">
         <f>_xlfn.DISPIMG("ID_54DAF5BED214466BBC185D077DB108F7",1)</f>
         <v>=DISPIMG("ID_54DAF5BED214466BBC185D077DB108F7",1)</v>
       </c>
     </row>
     <row r="25" ht="37" customHeight="1" spans="1:16">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="7"/>
       <c r="F25" s="4"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
+      <c r="G25" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
+      <c r="P25" s="14" t="str">
+        <f>_xlfn.DISPIMG("ID_F05DCBE9AA4948C1A4F8791A69F0466D",1)</f>
+        <v>=DISPIMG("ID_F05DCBE9AA4948C1A4F8791A69F0466D",1)</v>
+      </c>
     </row>
     <row r="26" ht="37" customHeight="1" spans="1:16">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="7"/>
       <c r="F26" s="4"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
+      <c r="G26" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" ht="37" customHeight="1" spans="1:16">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="P26" s="14" t="str">
+        <f>_xlfn.DISPIMG("ID_05EEE1B1EC2C430FBAC6E707CF2F7ED1",1)</f>
+        <v>=DISPIMG("ID_05EEE1B1EC2C430FBAC6E707CF2F7ED1",1)</v>
+      </c>
+    </row>
+    <row r="27" ht="37" customHeight="1" spans="1:17">
+      <c r="A27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="13"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
+      <c r="G27" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P27" s="14" t="str">
+        <f>_xlfn.DISPIMG("ID_8670CE2A04B84A3CBC23D16A2ACA0B53",1)</f>
+        <v>=DISPIMG("ID_8670CE2A04B84A3CBC23D16A2ACA0B53",1)</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="28" ht="37" customHeight="1" spans="1:16">
       <c r="A28" s="3"/>

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -579,11 +579,127 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="ID_61B6F34B990E4E9C9F549EF307D73847"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18871565" y="11087100"/>
+          <a:ext cx="12954000" cy="9525000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="ID_C0FBD3B25C0C44CA8D14D37D40DAB5EC"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18871565" y="13906500"/>
+          <a:ext cx="11258550" cy="9401175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="ID_BDCC4AF20B1B4567A53A244B9296EC79"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20760690" y="14376400"/>
+          <a:ext cx="11239500" cy="7705725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="ID_C9C4D65D091D4D439C3E616B28217BAB"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21041995" y="14846300"/>
+          <a:ext cx="11687175" cy="9344025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="100">
   <si>
     <t>Номер</t>
   </si>
@@ -591,6 +707,12 @@
     <t>rho(t) в 13 точках</t>
   </si>
   <si>
+    <t>Период (года)</t>
+  </si>
+  <si>
+    <t>Амплитуда %</t>
+  </si>
+  <si>
     <t>Угол центра перепада (градусов)</t>
   </si>
   <si>
@@ -750,27 +872,30 @@
     <t>не отличается от схемы первого порядка по времени</t>
   </si>
   <si>
+    <t>3.11 (ниже перезаписано)</t>
+  </si>
+  <si>
+    <t>0-30</t>
+  </si>
+  <si>
+    <t>есть в носике, что-то странное</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>1800000</t>
+  </si>
+  <si>
     <t>3.11</t>
   </si>
   <si>
-    <t>0-30</t>
-  </si>
-  <si>
-    <t>есть в носике, что-то странное</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>2.2</t>
-  </si>
-  <si>
-    <t>4.1</t>
-  </si>
-  <si>
-    <t>1800000</t>
-  </si>
-  <si>
     <t>40</t>
   </si>
   <si>
@@ -829,6 +954,51 @@
   </si>
   <si>
     <t>Неустойчивости нет, возможно разрешения не хватает</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>стабилизации нет</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3.15</t>
+  </si>
+  <si>
+    <t>нет атомов за TS</t>
+  </si>
+  <si>
+    <t>потрясающая картина вихрей</t>
+  </si>
+  <si>
+    <t>3.16</t>
+  </si>
+  <si>
+    <t>1.8 (только плотность)</t>
+  </si>
+  <si>
+    <t>перепад плотности оставил как есть, а скорость не трогал</t>
   </si>
 </sst>
 </file>
@@ -841,7 +1011,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -858,6 +1028,13 @@
     </font>
     <font>
       <sz val="16"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1054,13 +1231,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="5" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.25"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1390,137 +1567,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1552,28 +1729,34 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1895,29 +2078,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="16.3363636363636" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20" style="1" customWidth="1"/>
     <col min="2" max="5" width="6.02727272727273" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6909090909091" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.2181818181818" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34.5545454545455" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.4454545454545" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.3363636363636" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.4454545454545" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.3363636363636" style="1" customWidth="1"/>
-    <col min="14" max="14" width="27.5545454545455" style="1" customWidth="1"/>
-    <col min="15" max="15" width="31.4454545454545" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.4545454545455" style="1" customWidth="1"/>
-    <col min="17" max="17" width="81.2727272727273" style="1" customWidth="1"/>
-    <col min="18" max="18" width="63.2636363636364" style="1" customWidth="1"/>
-    <col min="19" max="21" width="16.3363636363636" style="1" customWidth="1"/>
-    <col min="22" max="27" width="16.3363636363636" customWidth="1"/>
+    <col min="6" max="7" width="11.6909090909091" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.7181818181818" style="2" customWidth="1"/>
+    <col min="9" max="9" width="35.2181818181818" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7" style="1" customWidth="1"/>
+    <col min="11" max="11" width="34.5545454545455" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.4454545454545" style="1" customWidth="1"/>
+    <col min="13" max="13" width="23.3363636363636" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.4454545454545" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.3363636363636" style="1" customWidth="1"/>
+    <col min="16" max="16" width="27.5545454545455" style="1" customWidth="1"/>
+    <col min="17" max="17" width="31.4454545454545" style="1" customWidth="1"/>
+    <col min="18" max="18" width="16.4545454545455" style="1" customWidth="1"/>
+    <col min="19" max="19" width="81.2727272727273" style="1" customWidth="1"/>
+    <col min="20" max="20" width="63.2636363636364" style="1" customWidth="1"/>
+    <col min="21" max="23" width="16.3363636363636" style="1" customWidth="1"/>
+    <col min="24" max="29" width="16.3363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="79" customHeight="1" spans="1:17">
+    <row r="1" ht="79" customHeight="1" spans="1:19">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1928,10 +2112,10 @@
       <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
@@ -1958,34 +2142,36 @@
       <c r="P1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="R1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" ht="37" customHeight="1" spans="1:16">
+    <row r="2" ht="37" customHeight="1" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>18</v>
@@ -1996,34 +2182,36 @@
       <c r="O2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P2" s="3"/>
+      <c r="P2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" s="3"/>
     </row>
-    <row r="3" ht="37" customHeight="1" spans="1:19">
+    <row r="3" ht="37" customHeight="1" spans="1:21">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
       <c r="I3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>18</v>
@@ -2034,41 +2222,43 @@
       <c r="O3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="3"/>
-      <c r="R3" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="17" t="str">
+      <c r="P3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" s="3"/>
+      <c r="T3" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="U3" s="18" t="str">
         <f>_xlfn.DISPIMG("ID_2DC6207669014A37BFB9BE39DC187DCE",1)</f>
         <v>=DISPIMG("ID_2DC6207669014A37BFB9BE39DC187DCE",1)</v>
       </c>
     </row>
-    <row r="4" ht="37" customHeight="1" spans="1:16">
+    <row r="4" ht="37" customHeight="1" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>18</v>
@@ -2079,31 +2269,33 @@
       <c r="O4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P4" s="3"/>
+      <c r="P4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R4" s="3"/>
     </row>
-    <row r="5" ht="37" customHeight="1" spans="1:16">
+    <row r="5" ht="37" customHeight="1" spans="1:18">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
       <c r="I5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>28</v>
@@ -2112,429 +2304,449 @@
         <v>18</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P5" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_AAAED62E82D54B409AB5C8B0C7DD6A82",1)</f>
         <v>=DISPIMG("ID_AAAED62E82D54B409AB5C8B0C7DD6A82",1)</v>
       </c>
     </row>
-    <row r="6" ht="37" customHeight="1" spans="1:16">
+    <row r="6" ht="37" customHeight="1" spans="1:18">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>26</v>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P6" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_4CFD75D374CE4DDE9E03BA4DC092D744",1)</f>
         <v>=DISPIMG("ID_4CFD75D374CE4DDE9E03BA4DC092D744",1)</v>
       </c>
     </row>
-    <row r="7" ht="37" customHeight="1" spans="1:17">
+    <row r="7" ht="37" customHeight="1" spans="1:19">
       <c r="A7" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>26</v>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P7" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_6DCA3A3E153C4171953BC0544CE3C76A",1)</f>
         <v>=DISPIMG("ID_6DCA3A3E153C4171953BC0544CE3C76A",1)</v>
       </c>
-      <c r="Q7" s="18" t="s">
-        <v>33</v>
+      <c r="S7" s="20" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="8" ht="37" customHeight="1" spans="1:17">
+    <row r="8" ht="37" customHeight="1" spans="1:19">
       <c r="A8" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="6"/>
       <c r="E8" s="7"/>
       <c r="F8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="11" t="s">
         <v>37</v>
       </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="L8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P8" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_49006A477D2349A0BE5661F7511B2CBC",1)</f>
         <v>=DISPIMG("ID_49006A477D2349A0BE5661F7511B2CBC",1)</v>
       </c>
-      <c r="Q8" s="1" t="s">
-        <v>38</v>
+      <c r="S8" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="9" ht="37" customHeight="1" spans="1:16">
+    <row r="9" ht="37" customHeight="1" spans="1:18">
       <c r="A9" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>26</v>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P9" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_4322BD9D201E4A40820FC7B99B813840",1)</f>
         <v>=DISPIMG("ID_4322BD9D201E4A40820FC7B99B813840",1)</v>
       </c>
     </row>
-    <row r="10" ht="37" customHeight="1" spans="1:17">
+    <row r="10" ht="37" customHeight="1" spans="1:19">
       <c r="A10" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>26</v>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>18</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P10" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_02B3F99283104BCBB532A5A0354AB72C",1)</f>
         <v>=DISPIMG("ID_02B3F99283104BCBB532A5A0354AB72C",1)</v>
       </c>
-      <c r="Q10" s="18" t="s">
-        <v>45</v>
+      <c r="S10" s="20" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="11" ht="37" customHeight="1" spans="1:17">
+    <row r="11" ht="37" customHeight="1" spans="1:19">
       <c r="A11" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
-      <c r="G11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>26</v>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="P11" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="R11" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_FE861988B73846E0B38C47E32EB5393F",1)</f>
         <v>=DISPIMG("ID_FE861988B73846E0B38C47E32EB5393F",1)</v>
       </c>
-      <c r="Q11" s="18"/>
+      <c r="S11" s="20"/>
     </row>
-    <row r="12" ht="37" customHeight="1" spans="1:16">
+    <row r="12" ht="37" customHeight="1" spans="1:18">
       <c r="A12" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>16</v>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="P12" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="R12" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_B6639CE39850471191E748FA5694FB6F",1)</f>
         <v>=DISPIMG("ID_B6639CE39850471191E748FA5694FB6F",1)</v>
       </c>
     </row>
-    <row r="13" ht="37" customHeight="1" spans="1:17">
+    <row r="13" ht="37" customHeight="1" spans="1:19">
       <c r="A13" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="7"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>37</v>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P13" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_7C45C7571ED744B89C8B413974F434EA",1)</f>
         <v>=DISPIMG("ID_7C45C7571ED744B89C8B413974F434EA",1)</v>
       </c>
-      <c r="Q13" s="1" t="s">
-        <v>54</v>
+      <c r="S13" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1" spans="1:16">
+    <row r="14" ht="54" customHeight="1" spans="1:18">
       <c r="A14" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>26</v>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="P14" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="R14" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_6D09333D2B624D3AA8D9D1DBAAFF6749",1)</f>
         <v>=DISPIMG("ID_6D09333D2B624D3AA8D9D1DBAAFF6749",1)</v>
       </c>
     </row>
-    <row r="15" ht="37" customHeight="1" spans="1:16">
+    <row r="15" ht="37" customHeight="1" spans="1:18">
       <c r="A15" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="6"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>37</v>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>19</v>
@@ -2542,630 +2754,853 @@
       <c r="O15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P15" s="3"/>
+      <c r="P15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R15" s="3"/>
     </row>
-    <row r="16" ht="37" customHeight="1" spans="1:16">
+    <row r="16" ht="37" customHeight="1" spans="1:18">
       <c r="A16" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="6"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
-      <c r="G16" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>37</v>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M16" s="3" t="s">
-        <v>18</v>
+      <c r="M16" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P16" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" s="3"/>
     </row>
-    <row r="17" ht="37" customHeight="1" spans="1:16">
+    <row r="17" ht="37" customHeight="1" spans="1:18">
       <c r="A17" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="6"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" s="11" t="s">
         <v>37</v>
       </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="L17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
     </row>
-    <row r="18" ht="37" customHeight="1" spans="1:16">
+    <row r="18" ht="37" customHeight="1" spans="1:18">
       <c r="A18" s="11" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="7"/>
       <c r="F18" s="4"/>
-      <c r="G18" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>37</v>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
     </row>
-    <row r="19" ht="37" customHeight="1" spans="1:17">
+    <row r="19" ht="37" customHeight="1" spans="1:19">
       <c r="A19" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="4"/>
-      <c r="G19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>65</v>
-      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
       <c r="I19" s="3" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>37</v>
+        <v>68</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R19" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_F8652202BAD9483CA0345616A3ED7FD4",1)</f>
         <v>=DISPIMG("ID_F8652202BAD9483CA0345616A3ED7FD4",1)</v>
       </c>
-      <c r="Q19" s="1" t="s">
-        <v>66</v>
+      <c r="S19" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="20" ht="37" customHeight="1" spans="1:16">
+    <row r="20" ht="37" customHeight="1" spans="1:18">
       <c r="A20" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="12"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>65</v>
-      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
       <c r="I20" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L20" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>19</v>
+      <c r="K20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N20" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P20" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_3840878A904E4B56A2DD87192D35456F",1)</f>
         <v>=DISPIMG("ID_3840878A904E4B56A2DD87192D35456F",1)</v>
       </c>
     </row>
-    <row r="21" ht="37" customHeight="1" spans="1:17">
+    <row r="21" ht="37" customHeight="1" spans="1:19">
       <c r="A21" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
       <c r="I21" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L21" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N21" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P21" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_D3ACB0D6ED9E402EB08DE4311E6D85F2",1)</f>
         <v>=DISPIMG("ID_D3ACB0D6ED9E402EB08DE4311E6D85F2",1)</v>
       </c>
-      <c r="Q21" s="1" t="s">
-        <v>70</v>
+      <c r="S21" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="22" ht="37" customHeight="1" spans="1:16">
+    <row r="22" ht="37" customHeight="1" spans="1:18">
       <c r="A22" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="12"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
       <c r="I22" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L22" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>19</v>
+        <v>43</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N22" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P22" s="14" t="str">
+        <v>20</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_3A1B8F4BCF0C4B34AB3CE341C5ED6561",1)</f>
         <v>=DISPIMG("ID_3A1B8F4BCF0C4B34AB3CE341C5ED6561",1)</v>
       </c>
     </row>
-    <row r="23" ht="37" customHeight="1" spans="1:16">
-      <c r="A23" s="11" t="s">
-        <v>72</v>
+    <row r="23" ht="37" customHeight="1" spans="1:18">
+      <c r="A23" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="12"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
       <c r="I23" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O23" s="3"/>
-      <c r="P23" s="14"/>
+        <v>46</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N23" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="19" t="str">
+        <f>_xlfn.DISPIMG("ID_61B6F34B990E4E9C9F549EF307D73847",1)</f>
+        <v>=DISPIMG("ID_61B6F34B990E4E9C9F549EF307D73847",1)</v>
+      </c>
     </row>
-    <row r="24" ht="37" customHeight="1" spans="1:16">
+    <row r="24" ht="37" customHeight="1" spans="1:18">
       <c r="A24" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="12"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
       <c r="I24" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L24" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="14" t="str">
+        <v>77</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N24" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_54DAF5BED214466BBC185D077DB108F7",1)</f>
         <v>=DISPIMG("ID_54DAF5BED214466BBC185D077DB108F7",1)</v>
       </c>
     </row>
-    <row r="25" ht="37" customHeight="1" spans="1:16">
+    <row r="25" ht="37" customHeight="1" spans="1:18">
       <c r="A25" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="7"/>
       <c r="F25" s="4"/>
-      <c r="G25" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>37</v>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="14" t="str">
+        <v>32</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_F05DCBE9AA4948C1A4F8791A69F0466D",1)</f>
         <v>=DISPIMG("ID_F05DCBE9AA4948C1A4F8791A69F0466D",1)</v>
       </c>
     </row>
-    <row r="26" ht="37" customHeight="1" spans="1:16">
+    <row r="26" ht="37" customHeight="1" spans="1:18">
       <c r="A26" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="7"/>
       <c r="F26" s="4"/>
-      <c r="G26" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>37</v>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="14" t="str">
+        <v>32</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_05EEE1B1EC2C430FBAC6E707CF2F7ED1",1)</f>
         <v>=DISPIMG("ID_05EEE1B1EC2C430FBAC6E707CF2F7ED1",1)</v>
       </c>
     </row>
-    <row r="27" ht="37" customHeight="1" spans="1:17">
+    <row r="27" ht="37" customHeight="1" spans="1:19">
       <c r="A27" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="13"/>
+      <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>37</v>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P27" s="14" t="str">
+      <c r="P27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R27" s="19" t="str">
         <f>_xlfn.DISPIMG("ID_8670CE2A04B84A3CBC23D16A2ACA0B53",1)</f>
         <v>=DISPIMG("ID_8670CE2A04B84A3CBC23D16A2ACA0B53",1)</v>
       </c>
-      <c r="Q27" s="1" t="s">
-        <v>81</v>
+      <c r="S27" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="28" ht="37" customHeight="1" spans="1:16">
-      <c r="A28" s="3"/>
+    <row r="28" ht="37" customHeight="1" spans="1:18">
+      <c r="A28" s="4" t="s">
+        <v>85</v>
+      </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+      <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
     </row>
-    <row r="29" ht="37" customHeight="1" spans="1:16">
-      <c r="A29" s="3"/>
+    <row r="29" ht="37" customHeight="1" spans="1:18">
+      <c r="A29" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="19" t="str">
+        <f>_xlfn.DISPIMG("ID_C0FBD3B25C0C44CA8D14D37D40DAB5EC",1)</f>
+        <v>=DISPIMG("ID_C0FBD3B25C0C44CA8D14D37D40DAB5EC",1)</v>
+      </c>
     </row>
-    <row r="30" ht="37" customHeight="1" spans="1:16">
-      <c r="A30" s="3"/>
+    <row r="30" ht="37" customHeight="1" spans="1:19">
+      <c r="A30" s="4" t="s">
+        <v>87</v>
+      </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
+      <c r="G30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M30" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="19" t="str">
+        <f>_xlfn.DISPIMG("ID_BDCC4AF20B1B4567A53A244B9296EC79",1)</f>
+        <v>=DISPIMG("ID_BDCC4AF20B1B4567A53A244B9296EC79",1)</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="31" ht="37" customHeight="1" spans="1:16">
-      <c r="A31" s="3"/>
+    <row r="31" ht="37" customHeight="1" spans="1:18">
+      <c r="A31" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
+      <c r="G31" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M31" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="19" t="str">
+        <f>_xlfn.DISPIMG("ID_C9C4D65D091D4D439C3E616B28217BAB",1)</f>
+        <v>=DISPIMG("ID_C9C4D65D091D4D439C3E616B28217BAB",1)</v>
+      </c>
     </row>
-    <row r="32" ht="37" customHeight="1" spans="1:16">
-      <c r="A32" s="3"/>
+    <row r="32" ht="37" customHeight="1" spans="1:18">
+      <c r="A32" s="14" t="s">
+        <v>90</v>
+      </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
+      <c r="G32" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M32" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
     </row>
-    <row r="33" ht="37" customHeight="1" spans="1:16">
-      <c r="A33" s="3"/>
+    <row r="33" ht="37" customHeight="1" spans="1:18">
+      <c r="A33" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="4"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
+      <c r="G33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
     </row>
-    <row r="34" ht="37" customHeight="1" spans="1:16">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
+    <row r="34" ht="37" customHeight="1" spans="1:19">
+      <c r="A34" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M34" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P34" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="1" t="s">
+        <v>96</v>
+      </c>
     </row>
-    <row r="35" ht="37" customHeight="1" spans="1:16">
-      <c r="A35" s="3"/>
+    <row r="35" ht="37" customHeight="1" spans="1:19">
+      <c r="A35" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="36" ht="37" customHeight="1"/>
   </sheetData>

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10400"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1340,19 +1340,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1362,6 +1349,19 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1519,7 +1519,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1577,6 +1577,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1906,7 +1912,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1930,16 +1936,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1948,89 +1954,89 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2044,6 +2050,15 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2053,6 +2068,9 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2062,10 +2080,10 @@
     <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2074,34 +2092,19 @@
     <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2423,30 +2426,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="20" style="1" customWidth="1"/>
-    <col min="2" max="6" width="6.02727272727273" style="1" customWidth="1"/>
-    <col min="7" max="8" width="11.6909090909091" style="2" customWidth="1"/>
-    <col min="9" max="9" width="28.8272727272727" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.2181818181818" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.7" style="1" customWidth="1"/>
-    <col min="12" max="12" width="34.5545454545455" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.4454545454545" style="1" customWidth="1"/>
-    <col min="14" max="14" width="23.3363636363636" style="1" customWidth="1"/>
-    <col min="15" max="15" width="19.4454545454545" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.3363636363636" style="1" customWidth="1"/>
-    <col min="17" max="17" width="27.5545454545455" style="1" customWidth="1"/>
-    <col min="18" max="18" width="31.4454545454545" style="1" customWidth="1"/>
-    <col min="19" max="19" width="22.0727272727273" style="1" customWidth="1"/>
-    <col min="20" max="20" width="133.245454545455" style="1" customWidth="1"/>
-    <col min="21" max="21" width="63.2636363636364" style="1" customWidth="1"/>
-    <col min="22" max="24" width="16.3363636363636" style="1" customWidth="1"/>
-    <col min="25" max="30" width="16.3363636363636" customWidth="1"/>
+    <col min="2" max="6" width="6.02777777777778" style="1" customWidth="1"/>
+    <col min="7" max="8" width="11.6944444444444" style="2" customWidth="1"/>
+    <col min="9" max="9" width="28.8240740740741" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.2222222222222" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7037037037037" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34.5555555555556" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.4444444444444" style="1" customWidth="1"/>
+    <col min="14" max="14" width="23.3333333333333" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.4444444444444" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.3333333333333" style="1" customWidth="1"/>
+    <col min="17" max="17" width="27.5555555555556" style="1" customWidth="1"/>
+    <col min="18" max="18" width="31.4444444444444" style="1" customWidth="1"/>
+    <col min="19" max="19" width="22.0740740740741" style="1" customWidth="1"/>
+    <col min="20" max="20" width="133.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="63.2592592592593" style="1" customWidth="1"/>
+    <col min="22" max="24" width="16.3333333333333" style="1" customWidth="1"/>
+    <col min="25" max="30" width="16.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="79" customHeight="1" spans="1:20">
+    <row r="1" ht="79" customHeight="1" spans="1:22">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2498,7 +2501,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="37" customHeight="1" spans="1:19">
+    <row r="2" ht="37" customHeight="1" spans="1:22">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -2577,15 +2580,15 @@
         <v>22</v>
       </c>
       <c r="S3" s="3"/>
-      <c r="U3" s="20" t="s">
+      <c r="U3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="V3" s="21" t="str">
+      <c r="V3" s="6" t="str">
         <f>_xlfn.DISPIMG("ID_2DC6207669014A37BFB9BE39DC187DCE",1)</f>
         <v>=DISPIMG("ID_2DC6207669014A37BFB9BE39DC187DCE",1)</v>
       </c>
     </row>
-    <row r="4" ht="37" customHeight="1" spans="1:19">
+    <row r="4" ht="37" customHeight="1" spans="1:22">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
@@ -2626,7 +2629,7 @@
       </c>
       <c r="S4" s="3"/>
     </row>
-    <row r="5" ht="37" customHeight="1" spans="1:19">
+    <row r="5" ht="37" customHeight="1" spans="1:22">
       <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
@@ -2665,12 +2668,12 @@
       <c r="R5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S5" s="22" t="str">
+      <c r="S5" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_AAAED62E82D54B409AB5C8B0C7DD6A82",1)</f>
         <v>=DISPIMG("ID_AAAED62E82D54B409AB5C8B0C7DD6A82",1)</v>
       </c>
     </row>
-    <row r="6" ht="37" customHeight="1" spans="1:19">
+    <row r="6" ht="37" customHeight="1" spans="1:22">
       <c r="A6" s="3" t="s">
         <v>31</v>
       </c>
@@ -2709,20 +2712,20 @@
       <c r="R6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S6" s="22" t="str">
+      <c r="S6" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_4CFD75D374CE4DDE9E03BA4DC092D744",1)</f>
         <v>=DISPIMG("ID_4CFD75D374CE4DDE9E03BA4DC092D744",1)</v>
       </c>
     </row>
-    <row r="7" ht="37" customHeight="1" spans="1:20">
-      <c r="A7" s="5" t="s">
+    <row r="7" ht="37" customHeight="1" spans="1:22">
+      <c r="A7" s="8" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
+      <c r="C7" s="8"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -2753,22 +2756,22 @@
       <c r="R7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S7" s="22" t="str">
+      <c r="S7" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_6DCA3A3E153C4171953BC0544CE3C76A",1)</f>
         <v>=DISPIMG("ID_6DCA3A3E153C4171953BC0544CE3C76A",1)</v>
       </c>
-      <c r="T7" s="23" t="s">
+      <c r="T7" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" ht="37" customHeight="1" spans="1:20">
-      <c r="A8" s="8" t="s">
+    <row r="8" ht="37" customHeight="1" spans="1:22">
+      <c r="A8" s="12" t="s">
         <v>36</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
         <v>37</v>
@@ -2802,7 +2805,7 @@
       <c r="R8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S8" s="22" t="str">
+      <c r="S8" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_49006A477D2349A0BE5661F7511B2CBC",1)</f>
         <v>=DISPIMG("ID_49006A477D2349A0BE5661F7511B2CBC",1)</v>
       </c>
@@ -2810,11 +2813,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" ht="37" customHeight="1" spans="1:19">
-      <c r="A9" s="10" t="s">
+    <row r="9" ht="37" customHeight="1" spans="1:22">
+      <c r="A9" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="10"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -2849,16 +2852,16 @@
       <c r="R9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S9" s="22" t="str">
+      <c r="S9" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_4322BD9D201E4A40820FC7B99B813840",1)</f>
         <v>=DISPIMG("ID_4322BD9D201E4A40820FC7B99B813840",1)</v>
       </c>
     </row>
-    <row r="10" ht="37" customHeight="1" spans="1:20">
-      <c r="A10" s="10" t="s">
+    <row r="10" ht="37" customHeight="1" spans="1:22">
+      <c r="A10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="10"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -2893,26 +2896,26 @@
       <c r="R10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S10" s="22" t="str">
+      <c r="S10" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_02B3F99283104BCBB532A5A0354AB72C",1)</f>
         <v>=DISPIMG("ID_02B3F99283104BCBB532A5A0354AB72C",1)</v>
       </c>
-      <c r="T10" s="23" t="s">
+      <c r="T10" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" ht="37" customHeight="1" spans="1:20">
-      <c r="A11" s="11" t="s">
+    <row r="11" ht="37" customHeight="1" spans="1:22">
+      <c r="A11" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
       <c r="J11" s="4" t="s">
         <v>49</v>
       </c>
@@ -2940,18 +2943,18 @@
       <c r="R11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S11" s="22" t="str">
+      <c r="S11" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_FE861988B73846E0B38C47E32EB5393F",1)</f>
         <v>=DISPIMG("ID_FE861988B73846E0B38C47E32EB5393F",1)</v>
       </c>
-      <c r="T11" s="23"/>
-    </row>
-    <row r="12" ht="37" customHeight="1" spans="1:19">
-      <c r="A12" s="5" t="s">
+      <c r="T11" s="11"/>
+    </row>
+    <row r="12" ht="37" customHeight="1" spans="1:22">
+      <c r="A12" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
+      <c r="C12" s="8"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -2964,7 +2967,7 @@
       <c r="K12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="17" t="s">
         <v>53</v>
       </c>
       <c r="M12" s="3" t="s">
@@ -2985,19 +2988,19 @@
       <c r="R12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="S12" s="22" t="str">
+      <c r="S12" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_B6639CE39850471191E748FA5694FB6F",1)</f>
         <v>=DISPIMG("ID_B6639CE39850471191E748FA5694FB6F",1)</v>
       </c>
     </row>
-    <row r="13" ht="37" customHeight="1" spans="1:20">
+    <row r="13" ht="37" customHeight="1" spans="1:22">
       <c r="A13" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="9"/>
+      <c r="E13" s="13"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -3029,7 +3032,7 @@
       <c r="R13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S13" s="22" t="str">
+      <c r="S13" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_7C45C7571ED744B89C8B413974F434EA",1)</f>
         <v>=DISPIMG("ID_7C45C7571ED744B89C8B413974F434EA",1)</v>
       </c>
@@ -3037,7 +3040,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1" spans="1:19">
+    <row r="14" ht="54" customHeight="1" spans="1:22">
       <c r="A14" s="4" t="s">
         <v>57</v>
       </c>
@@ -3076,18 +3079,18 @@
       <c r="R14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="S14" s="22" t="str">
+      <c r="S14" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_6D09333D2B624D3AA8D9D1DBAAFF6749",1)</f>
         <v>=DISPIMG("ID_6D09333D2B624D3AA8D9D1DBAAFF6749",1)</v>
       </c>
     </row>
-    <row r="15" ht="37" customHeight="1" spans="1:19">
-      <c r="A15" s="8" t="s">
+    <row r="15" ht="37" customHeight="1" spans="1:22">
+      <c r="A15" s="12" t="s">
         <v>60</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="8"/>
+      <c r="D15" s="12"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -3122,13 +3125,13 @@
       </c>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" ht="37" customHeight="1" spans="1:19">
-      <c r="A16" s="8" t="s">
+    <row r="16" ht="37" customHeight="1" spans="1:22">
+      <c r="A16" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="8"/>
+      <c r="D16" s="12"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -3163,13 +3166,13 @@
       </c>
       <c r="S16" s="3"/>
     </row>
-    <row r="17" ht="37" customHeight="1" spans="1:19">
-      <c r="A17" s="8" t="s">
+    <row r="17" ht="37" customHeight="1" spans="1:20">
+      <c r="A17" s="12" t="s">
         <v>62</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="12"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4" t="s">
@@ -3204,14 +3207,14 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
     </row>
-    <row r="18" ht="37" customHeight="1" spans="1:19">
+    <row r="18" ht="37" customHeight="1" spans="1:20">
       <c r="A18" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="9"/>
+      <c r="E18" s="13"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -3282,7 +3285,7 @@
       <c r="R19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S19" s="22" t="str">
+      <c r="S19" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_F8652202BAD9483CA0345616A3ED7FD4",1)</f>
         <v>=DISPIMG("ID_F8652202BAD9483CA0345616A3ED7FD4",1)</v>
       </c>
@@ -3290,14 +3293,14 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" ht="37" customHeight="1" spans="1:19">
-      <c r="A20" s="13" t="s">
+    <row r="20" ht="37" customHeight="1" spans="1:20">
+      <c r="A20" s="17" t="s">
         <v>70</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="14"/>
+      <c r="E20" s="18"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -3317,7 +3320,7 @@
       <c r="N20" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O20" s="18" t="s">
+      <c r="O20" s="19" t="s">
         <v>71</v>
       </c>
       <c r="P20" s="3" t="s">
@@ -3329,7 +3332,7 @@
       <c r="R20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S20" s="22" t="str">
+      <c r="S20" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_3840878A904E4B56A2DD87192D35456F",1)</f>
         <v>=DISPIMG("ID_3840878A904E4B56A2DD87192D35456F",1)</v>
       </c>
@@ -3341,8 +3344,8 @@
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="7"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="10"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -3361,7 +3364,7 @@
       <c r="N21" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O21" s="18" t="s">
+      <c r="O21" s="19" t="s">
         <v>71</v>
       </c>
       <c r="P21" s="3" t="s">
@@ -3373,7 +3376,7 @@
       <c r="R21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S21" s="22" t="str">
+      <c r="S21" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_D3ACB0D6ED9E402EB08DE4311E6D85F2",1)</f>
         <v>=DISPIMG("ID_D3ACB0D6ED9E402EB08DE4311E6D85F2",1)</v>
       </c>
@@ -3381,14 +3384,14 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" ht="37" customHeight="1" spans="1:19">
+    <row r="22" ht="37" customHeight="1" spans="1:20">
       <c r="A22" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="14"/>
+      <c r="E22" s="18"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -3408,7 +3411,7 @@
       <c r="N22" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O22" s="18" t="s">
+      <c r="O22" s="19" t="s">
         <v>71</v>
       </c>
       <c r="P22" s="3" t="s">
@@ -3420,19 +3423,19 @@
       <c r="R22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S22" s="22" t="str">
+      <c r="S22" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_3A1B8F4BCF0C4B34AB3CE341C5ED6561",1)</f>
         <v>=DISPIMG("ID_3A1B8F4BCF0C4B34AB3CE341C5ED6561",1)</v>
       </c>
     </row>
-    <row r="23" ht="37" customHeight="1" spans="1:19">
+    <row r="23" ht="37" customHeight="1" spans="1:20">
       <c r="A23" s="4" t="s">
         <v>75</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="14"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -3452,7 +3455,7 @@
       <c r="N23" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O23" s="18" t="s">
+      <c r="O23" s="19" t="s">
         <v>71</v>
       </c>
       <c r="P23" s="3" t="s">
@@ -3462,19 +3465,19 @@
         <v>21</v>
       </c>
       <c r="R23" s="3"/>
-      <c r="S23" s="22" t="str">
+      <c r="S23" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_61B6F34B990E4E9C9F549EF307D73847",1)</f>
         <v>=DISPIMG("ID_61B6F34B990E4E9C9F549EF307D73847",1)</v>
       </c>
     </row>
-    <row r="24" ht="37" customHeight="1" spans="1:19">
+    <row r="24" ht="37" customHeight="1" spans="1:20">
       <c r="A24" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="14"/>
+      <c r="E24" s="18"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -3494,7 +3497,7 @@
       <c r="N24" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O24" s="18" t="s">
+      <c r="O24" s="19" t="s">
         <v>71</v>
       </c>
       <c r="P24" s="3" t="s">
@@ -3504,19 +3507,19 @@
         <v>21</v>
       </c>
       <c r="R24" s="3"/>
-      <c r="S24" s="22" t="str">
+      <c r="S24" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_54DAF5BED214466BBC185D077DB108F7",1)</f>
         <v>=DISPIMG("ID_54DAF5BED214466BBC185D077DB108F7",1)</v>
       </c>
     </row>
-    <row r="25" ht="37" customHeight="1" spans="1:19">
+    <row r="25" ht="37" customHeight="1" spans="1:20">
       <c r="A25" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="9"/>
+      <c r="E25" s="13"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -3546,19 +3549,19 @@
         <v>21</v>
       </c>
       <c r="R25" s="3"/>
-      <c r="S25" s="22" t="str">
+      <c r="S25" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_F05DCBE9AA4948C1A4F8791A69F0466D",1)</f>
         <v>=DISPIMG("ID_F05DCBE9AA4948C1A4F8791A69F0466D",1)</v>
       </c>
     </row>
-    <row r="26" ht="37" customHeight="1" spans="1:19">
+    <row r="26" ht="37" customHeight="1" spans="1:20">
       <c r="A26" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="9"/>
+      <c r="E26" s="13"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -3588,7 +3591,7 @@
         <v>21</v>
       </c>
       <c r="R26" s="3"/>
-      <c r="S26" s="22" t="str">
+      <c r="S26" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_05EEE1B1EC2C430FBAC6E707CF2F7ED1",1)</f>
         <v>=DISPIMG("ID_05EEE1B1EC2C430FBAC6E707CF2F7ED1",1)</v>
       </c>
@@ -3632,7 +3635,7 @@
       <c r="R27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="S27" s="22" t="str">
+      <c r="S27" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_8670CE2A04B84A3CBC23D16A2ACA0B53",1)</f>
         <v>=DISPIMG("ID_8670CE2A04B84A3CBC23D16A2ACA0B53",1)</v>
       </c>
@@ -3640,8 +3643,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" ht="37" customHeight="1" spans="1:19">
-      <c r="A28" s="4" t="s">
+    <row r="28" ht="37" customHeight="1" spans="1:20">
+      <c r="A28" s="20" t="s">
         <v>85</v>
       </c>
       <c r="B28" s="3"/>
@@ -3679,7 +3682,7 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
-    <row r="29" ht="37" customHeight="1" spans="1:19">
+    <row r="29" ht="37" customHeight="1" spans="1:20">
       <c r="A29" s="4" t="s">
         <v>86</v>
       </c>
@@ -3716,7 +3719,7 @@
         <v>21</v>
       </c>
       <c r="R29" s="3"/>
-      <c r="S29" s="22" t="str">
+      <c r="S29" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_C0FBD3B25C0C44CA8D14D37D40DAB5EC",1)</f>
         <v>=DISPIMG("ID_C0FBD3B25C0C44CA8D14D37D40DAB5EC",1)</v>
       </c>
@@ -3731,10 +3734,10 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="15" t="s">
+      <c r="H30" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" s="21" t="s">
         <v>46</v>
       </c>
       <c r="J30" s="3" t="s">
@@ -3762,7 +3765,7 @@
         <v>21</v>
       </c>
       <c r="R30" s="3"/>
-      <c r="S30" s="22" t="str">
+      <c r="S30" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_BDCC4AF20B1B4567A53A244B9296EC79",1)</f>
         <v>=DISPIMG("ID_BDCC4AF20B1B4567A53A244B9296EC79",1)</v>
       </c>
@@ -3770,7 +3773,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" ht="37" customHeight="1" spans="1:19">
+    <row r="31" ht="37" customHeight="1" spans="1:20">
       <c r="A31" s="4" t="s">
         <v>89</v>
       </c>
@@ -3780,10 +3783,10 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="15" t="s">
+      <c r="H31" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="I31" s="21" t="s">
         <v>34</v>
       </c>
       <c r="J31" s="3" t="s">
@@ -3811,12 +3814,12 @@
         <v>21</v>
       </c>
       <c r="R31" s="3"/>
-      <c r="S31" s="22" t="str">
+      <c r="S31" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_C9C4D65D091D4D439C3E616B28217BAB",1)</f>
         <v>=DISPIMG("ID_C9C4D65D091D4D439C3E616B28217BAB",1)</v>
       </c>
     </row>
-    <row r="32" ht="37" customHeight="1" spans="1:19">
+    <row r="32" ht="37" customHeight="1" spans="1:20">
       <c r="A32" s="4" t="s">
         <v>90</v>
       </c>
@@ -3855,12 +3858,12 @@
       </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
-      <c r="S32" s="22" t="str">
+      <c r="S32" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_B4697F603E5040639414457DD3A26A12",1)</f>
         <v>=DISPIMG("ID_B4697F603E5040639414457DD3A26A12",1)</v>
       </c>
     </row>
-    <row r="33" ht="37" customHeight="1" spans="1:19">
+    <row r="33" ht="37" customHeight="1" spans="1:20">
       <c r="A33" s="4" t="s">
         <v>92</v>
       </c>
@@ -3899,12 +3902,12 @@
       </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
-      <c r="S33" s="22" t="str">
+      <c r="S33" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_6BC8FD8FB0D04132A093BA95446C2B53",1)</f>
         <v>=DISPIMG("ID_6BC8FD8FB0D04132A093BA95446C2B53",1)</v>
       </c>
     </row>
-    <row r="34" ht="45" customHeight="1" spans="1:19">
+    <row r="34" ht="45" customHeight="1" spans="1:20">
       <c r="A34" s="4" t="s">
         <v>94</v>
       </c>
@@ -3943,12 +3946,12 @@
       </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
-      <c r="S34" s="22" t="str">
+      <c r="S34" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_FF2E2B0E719546D9AA6D48D0C0E18B61",1)</f>
         <v>=DISPIMG("ID_FF2E2B0E719546D9AA6D48D0C0E18B61",1)</v>
       </c>
     </row>
-    <row r="35" ht="45" customHeight="1" spans="1:19">
+    <row r="35" ht="45" customHeight="1" spans="1:20">
       <c r="A35" s="4" t="s">
         <v>96</v>
       </c>
@@ -3989,7 +3992,7 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
     </row>
-    <row r="36" ht="45" customHeight="1" spans="1:19">
+    <row r="36" ht="45" customHeight="1" spans="1:20">
       <c r="A36" s="4" t="s">
         <v>98</v>
       </c>
@@ -4030,7 +4033,7 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
     </row>
-    <row r="37" ht="45" customHeight="1" spans="1:19">
+    <row r="37" ht="45" customHeight="1" spans="1:20">
       <c r="A37" s="4" t="s">
         <v>100</v>
       </c>
@@ -4078,8 +4081,8 @@
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="7"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="10"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
@@ -4104,11 +4107,11 @@
       <c r="P38" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Q38" s="24" t="s">
+      <c r="Q38" s="22" t="s">
         <v>103</v>
       </c>
       <c r="R38" s="3"/>
-      <c r="S38" s="22" t="str">
+      <c r="S38" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_24671931C21B4D7DBB8D2B54F6B675D6",1)</f>
         <v>=DISPIMG("ID_24671931C21B4D7DBB8D2B54F6B675D6",1)</v>
       </c>
@@ -4134,7 +4137,7 @@
       <c r="K39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="19" t="s">
+      <c r="L39" s="23" t="s">
         <v>106</v>
       </c>
       <c r="M39" s="3" t="s">
@@ -4153,7 +4156,7 @@
         <v>21</v>
       </c>
       <c r="R39" s="3"/>
-      <c r="S39" s="22" t="str">
+      <c r="S39" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_24C3BE2745B24940BCB18141774E4E1D",1)</f>
         <v>=DISPIMG("ID_24C3BE2745B24940BCB18141774E4E1D",1)</v>
       </c>
@@ -4161,7 +4164,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="40" ht="61" customHeight="1" spans="1:19">
+    <row r="40" ht="61" customHeight="1" spans="1:20">
       <c r="A40" s="4" t="s">
         <v>108</v>
       </c>
@@ -4198,7 +4201,7 @@
         <v>110</v>
       </c>
       <c r="R40" s="3"/>
-      <c r="S40" s="22" t="str">
+      <c r="S40" s="7" t="str">
         <f>_xlfn.DISPIMG("ID_FB602AFCED944FE5A9F6046FE878B8FB",1)</f>
         <v>=DISPIMG("ID_FB602AFCED944FE5A9F6046FE878B8FB",1)</v>
       </c>
@@ -4221,7 +4224,7 @@
       <c r="K41" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L41" s="19" t="s">
+      <c r="L41" s="23" t="s">
         <v>106</v>
       </c>
       <c r="M41" s="3" t="s">
@@ -4236,11 +4239,11 @@
       <c r="P41" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Q41" s="19" t="s">
+      <c r="Q41" s="23" t="s">
         <v>110</v>
       </c>
       <c r="R41" s="3"/>
-      <c r="S41" s="21" t="str">
+      <c r="S41" s="6" t="str">
         <f>_xlfn.DISPIMG("ID_8FB478083FCD466684C3DF6EDED92850",1)</f>
         <v>=DISPIMG("ID_8FB478083FCD466684C3DF6EDED92850",1)</v>
       </c>
@@ -4248,7 +4251,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" ht="87" customHeight="1" spans="1:19">
+    <row r="42" ht="87" customHeight="1" spans="1:20">
       <c r="A42" s="4" t="s">
         <v>113</v>
       </c>
@@ -4287,7 +4290,7 @@
       <c r="R42" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S42" s="21" t="str">
+      <c r="S42" s="6" t="str">
         <f>_xlfn.DISPIMG("ID_FD18B3E38FD14917BD88AE6EA643AF38",1)</f>
         <v>=DISPIMG("ID_FD18B3E38FD14917BD88AE6EA643AF38",1)</v>
       </c>
@@ -4299,7 +4302,7 @@
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="6"/>
+      <c r="E43" s="9"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -4335,15 +4338,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="44" ht="52" customHeight="1" spans="1:18">
+    <row r="44" ht="52" customHeight="1" spans="1:20">
       <c r="A44" s="3" t="s">
         <v>118</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="7"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="10"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -4375,14 +4378,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" ht="52" customHeight="1" spans="1:18">
+    <row r="45" ht="52" customHeight="1" spans="1:20">
       <c r="A45" s="3" t="s">
         <v>119</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="6"/>
+      <c r="E45" s="9"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -4397,15 +4400,15 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
     </row>
-    <row r="46" ht="54" customHeight="1" spans="1:18">
+    <row r="46" ht="54" customHeight="1" spans="1:20">
       <c r="A46" s="3" t="s">
         <v>120</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="7"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="10"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -4437,13 +4440,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" ht="54" customHeight="1" spans="1:18">
+    <row r="47" ht="54" customHeight="1" spans="1:20">
       <c r="A47" s="4" t="s">
         <v>121</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="8"/>
+      <c r="D47" s="12"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -4477,13 +4480,13 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" ht="40" customHeight="1" spans="1:18">
+    <row r="48" ht="40" customHeight="1" spans="1:20">
       <c r="A48" s="4" t="s">
         <v>122</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
-      <c r="D48" s="8"/>
+      <c r="D48" s="12"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -4523,7 +4526,7 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
-      <c r="D49" s="8"/>
+      <c r="D49" s="12"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -4558,12 +4561,12 @@
       </c>
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:18">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="17" t="s">
         <v>123</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
-      <c r="D50" s="8"/>
+      <c r="D50" s="12"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
@@ -4598,12 +4601,12 @@
       </c>
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:18">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="17" t="s">
         <v>124</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
-      <c r="D51" s="8"/>
+      <c r="D51" s="12"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -4637,34 +4640,35 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" ht="35" customHeight="1" spans="1:18">
-      <c r="A52" s="16" t="s">
+    <row r="52" ht="56" customHeight="1" spans="1:18">
+      <c r="A52" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="16" t="s">
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="K52" s="16" t="s">
+      <c r="K52" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="L52" s="16" t="s">
+      <c r="L52" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
-      <c r="O52" s="16"/>
-      <c r="P52" s="16"/>
-      <c r="Q52" s="16"/>
-      <c r="R52" s="16"/>
-    </row>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" ht="56" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -2036,7 +2036,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2093,6 +2093,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3219,7 +3222,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="14" t="s">
         <v>65</v>
       </c>
       <c r="K18" s="4" t="s">
@@ -3524,7 +3527,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="14" t="s">
         <v>79</v>
       </c>
       <c r="K25" s="4" t="s">
@@ -3566,7 +3569,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="4" t="s">
+      <c r="J26" s="14" t="s">
         <v>81</v>
       </c>
       <c r="K26" s="4" t="s">
@@ -3608,7 +3611,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="20" t="s">
         <v>83</v>
       </c>
       <c r="K27" s="4" t="s">
@@ -3644,7 +3647,7 @@
       </c>
     </row>
     <row r="28" ht="37" customHeight="1" spans="1:20">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="21" t="s">
         <v>85</v>
       </c>
       <c r="B28" s="3"/>
@@ -3734,10 +3737,10 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="21" t="s">
+      <c r="H30" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="21" t="s">
+      <c r="I30" s="22" t="s">
         <v>46</v>
       </c>
       <c r="J30" s="3" t="s">
@@ -3783,10 +3786,10 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="21" t="s">
+      <c r="H31" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="I31" s="21" t="s">
+      <c r="I31" s="22" t="s">
         <v>34</v>
       </c>
       <c r="J31" s="3" t="s">
@@ -4107,7 +4110,7 @@
       <c r="P38" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Q38" s="22" t="s">
+      <c r="Q38" s="23" t="s">
         <v>103</v>
       </c>
       <c r="R38" s="3"/>
@@ -4137,7 +4140,7 @@
       <c r="K39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="23" t="s">
+      <c r="L39" s="24" t="s">
         <v>106</v>
       </c>
       <c r="M39" s="3" t="s">
@@ -4224,7 +4227,7 @@
       <c r="K41" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L41" s="23" t="s">
+      <c r="L41" s="24" t="s">
         <v>106</v>
       </c>
       <c r="M41" s="3" t="s">
@@ -4239,7 +4242,7 @@
       <c r="P41" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Q41" s="23" t="s">
+      <c r="Q41" s="24" t="s">
         <v>110</v>
       </c>
       <c r="R41" s="3"/>
